--- a/Tools_and_Utilities/dashboards/OSS_SLU_CICD_Dashboard.xlsx
+++ b/Tools_and_Utilities/dashboards/OSS_SLU_CICD_Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danyu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sluedu-my.sharepoint.com/personal/henry_wang_slu_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC358F9F-2DE8-47BD-9A65-855F4550A089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E43FF807-5A23-4C76-B966-4D0C7776861F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OSS_SLU_CICD_Dashboard" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="119">
   <si>
     <t>Project_Name</t>
   </si>
@@ -143,6 +143,30 @@
     <t>https://github.com/oss-slu/dads</t>
   </si>
   <si>
+    <t>Digital Bone Box</t>
+  </si>
+  <si>
+    <t>https://github.com/oss-slu/DigitalBoneBox</t>
+  </si>
+  <si>
+    <t>Hybrid CI/CD</t>
+  </si>
+  <si>
+    <t>Mehul</t>
+  </si>
+  <si>
+    <t>Drone World</t>
+  </si>
+  <si>
+    <t>https://github.com/oss-slu/DroneWorld</t>
+  </si>
+  <si>
+    <t>GradEval360</t>
+  </si>
+  <si>
+    <t>https://github.com/oss-slu/GradEval360</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
@@ -152,30 +176,6 @@
     <t>Not assigned</t>
   </si>
   <si>
-    <t>Digital Bone Box</t>
-  </si>
-  <si>
-    <t>https://github.com/oss-slu/DigitalBoneBox</t>
-  </si>
-  <si>
-    <t>Hybrid CI/CD</t>
-  </si>
-  <si>
-    <t>Mehul</t>
-  </si>
-  <si>
-    <t>Drone World</t>
-  </si>
-  <si>
-    <t>https://github.com/oss-slu/DroneWorld</t>
-  </si>
-  <si>
-    <t>GradEval360</t>
-  </si>
-  <si>
-    <t>https://github.com/oss-slu/GradEval360</t>
-  </si>
-  <si>
     <t>iperf</t>
   </si>
   <si>
@@ -188,7 +188,7 @@
     <t>https://github.com/oss-slu/TheHealthApp</t>
   </si>
   <si>
-    <t>Requesting Help</t>
+    <t>Only uses CodeQL and Dependabot, more action needed</t>
   </si>
   <si>
     <t>IRIS</t>
@@ -197,6 +197,9 @@
     <t>https://github.com/oss-slu/image-recognition-integration-system/</t>
   </si>
   <si>
+    <t>Deprecated project</t>
+  </si>
+  <si>
     <t>MaterialDerailleur</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
   </si>
   <si>
     <t>https://github.com/oss-slu/mechatronics-vr</t>
+  </si>
+  <si>
+    <t>Unable to fully implement CI/CD workflow, but actions recommended for future consideration</t>
   </si>
   <si>
     <t>Mithridatium</t>
@@ -300,12 +306,6 @@
 https://github.com/oss-slu/lrda_mobile</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Pautler </t>
-  </si>
-  <si>
     <t>mostly CI/CD implemented for testing</t>
   </si>
   <si>
@@ -364,6 +364,9 @@
   </si>
   <si>
     <t>In progress</t>
+  </si>
+  <si>
+    <t>Requesting Help</t>
   </si>
   <si>
     <t>Negative</t>
@@ -397,7 +400,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,10 +529,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -818,23 +817,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K72"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="62.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="30.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.453125" customWidth="1"/>
+    <col min="9" max="9" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.42578125" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -869,7 +868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
@@ -898,10 +897,10 @@
         <v>18</v>
       </c>
       <c r="K2" s="1">
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="7" t="s">
         <v>19</v>
       </c>
@@ -933,7 +932,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11">
       <c r="A4" s="7" t="s">
         <v>25</v>
       </c>
@@ -962,7 +961,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11">
       <c r="A5" s="7" t="s">
         <v>29</v>
       </c>
@@ -994,8 +993,8 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -1005,30 +1004,30 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E6" t="s">
+      <c r="B7" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -1040,24 +1039,24 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
         <v>31</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K7" s="1">
         <v>45993</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11">
       <c r="A8" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
@@ -1081,36 +1080,36 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" t="s">
         <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" t="s">
-        <v>37</v>
       </c>
       <c r="K9" s="1">
         <v>46057</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1121,26 +1120,26 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K10" s="1">
         <v>46057</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:11">
+      <c r="A11" s="7" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1150,175 +1149,184 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" t="s">
         <v>50</v>
       </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11" t="s">
-        <v>37</v>
-      </c>
       <c r="K11" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
         <v>51</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
       </c>
+      <c r="J12" t="s">
+        <v>53</v>
+      </c>
       <c r="K12" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K13" s="1">
         <v>46057</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>55</v>
+    <row r="14" spans="1:11">
+      <c r="A14" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>58</v>
       </c>
       <c r="K14" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K15" s="1">
         <v>46057</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11">
       <c r="A16" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G16" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K16" s="1">
         <v>46057</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11">
       <c r="A17" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -1336,47 +1344,47 @@
         <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K17" s="1">
         <v>45993</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K18" s="1">
         <v>46057</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11">
       <c r="A19" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
@@ -1400,44 +1408,44 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G20" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K20" s="1">
         <v>46057</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11">
       <c r="A21" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
         <v>13</v>
@@ -1458,41 +1466,41 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>71</v>
+    <row r="22" spans="1:11">
+      <c r="A22" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I22" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="K22" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
@@ -1504,53 +1512,53 @@
         <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s">
         <v>16</v>
       </c>
       <c r="I23" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K23" s="1">
         <v>45993</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11">
       <c r="A24" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K24" s="1">
         <v>46057</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11">
       <c r="A25" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -1562,13 +1570,13 @@
         <v>14</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G25" t="s">
         <v>27</v>
       </c>
       <c r="H25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s">
         <v>28</v>
@@ -1577,12 +1585,12 @@
         <v>45943</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11">
       <c r="A26" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -1609,47 +1617,50 @@
         <v>45969</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>83</v>
+    <row r="27" spans="1:11">
+      <c r="A27" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G27" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
       </c>
+      <c r="J27" t="s">
+        <v>32</v>
+      </c>
       <c r="K27" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="32.1">
       <c r="A28" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
         <v>14</v>
@@ -1661,7 +1672,7 @@
         <v>16</v>
       </c>
       <c r="I28" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="J28" t="s">
         <v>89</v>
@@ -1670,10 +1681,10 @@
         <v>46076</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11">
       <c r="B29" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6">
       <c r="A35" s="4" t="s">
         <v>90</v>
       </c>
@@ -1687,7 +1698,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -1695,13 +1706,13 @@
         <v>94</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D36" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -1709,18 +1720,18 @@
         <v>95</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D37" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6">
       <c r="A43" s="10" t="s">
         <v>97</v>
       </c>
@@ -1729,10 +1740,10 @@
       </c>
       <c r="F43" s="13">
         <f>(7+C36+C37)/27</f>
-        <v>0.48148148148148145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="10" t="s">
         <v>99</v>
       </c>
@@ -1743,7 +1754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6">
       <c r="A45" s="10" t="s">
         <v>101</v>
       </c>
@@ -1752,10 +1763,10 @@
       </c>
       <c r="F45">
         <f>(C36+C37)/2</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" s="4" t="s">
         <v>103</v>
       </c>
@@ -1766,18 +1777,18 @@
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3">
       <c r="A50" s="5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3">
       <c r="A51" s="5" t="s">
         <v>14</v>
       </c>
@@ -1788,105 +1799,105 @@
         <v>108</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3">
       <c r="A52" s="5" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3">
       <c r="A55" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B55" s="5"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3">
       <c r="A56" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3">
       <c r="A60" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3">
       <c r="A64" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1">
       <c r="A65" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1">
       <c r="A66" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1">
       <c r="A67" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
       <c r="A68" s="4"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1">
       <c r="A72" s="5"/>
     </row>
   </sheetData>
@@ -1929,30 +1940,16 @@
     <hyperlink ref="B23" r:id="rId16" xr:uid="{17DB390E-390A-3441-9DA6-BD5D3D810401}"/>
     <hyperlink ref="B26" r:id="rId17" xr:uid="{3A661029-E8B8-4B47-9161-54941B4A7270}"/>
     <hyperlink ref="B27" r:id="rId18" xr:uid="{28AC3E3B-C802-437E-BA32-5285BD26B685}"/>
+    <hyperlink ref="B6" r:id="rId19" xr:uid="{72994E3D-52BD-48C9-A597-BCE94287AC2C}"/>
+    <hyperlink ref="B9" r:id="rId20" xr:uid="{DF01F2EB-3D08-FC4F-BDF9-78673EB0DF54}"/>
+    <hyperlink ref="B10" r:id="rId21" xr:uid="{4ED5A1CF-A55F-7C44-9D06-04497C6CD4F9}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6bfe3ee5-a6bf-4110-9b24-401e26a59a7c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC23B04C8E773C4BACEA69E6D98ABE69" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f7a966c730d7ab40742bba76d6e4e4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6bfe3ee5-a6bf-4110-9b24-401e26a59a7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="afa53b3af694b007294d89ea1ba90fbb" ns3:_="">
     <xsd:import namespace="6bfe3ee5-a6bf-4110-9b24-401e26a59a7c"/>
@@ -2134,44 +2131,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6bfe3ee5-a6bf-4110-9b24-401e26a59a7c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1C1BC48-780A-4332-8F2D-0975ADAD7847}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85B94D15-EECC-4855-921A-9B74260BB20F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E4CED61-1E02-4A88-B630-EF56B539545D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6bfe3ee5-a6bf-4110-9b24-401e26a59a7c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E4CED61-1E02-4A88-B630-EF56B539545D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85B94D15-EECC-4855-921A-9B74260BB20F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6bfe3ee5-a6bf-4110-9b24-401e26a59a7c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1C1BC48-780A-4332-8F2D-0975ADAD7847}"/>
 </file>